--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/56.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/56.xlsx
@@ -426,13 +426,13 @@
         <v>-16.14312185274201</v>
       </c>
       <c r="E2">
-        <v>-15.8888477230763</v>
+        <v>-14.36877653140038</v>
       </c>
       <c r="F2">
-        <v>2.614132709648074</v>
+        <v>4.631765655094357</v>
       </c>
       <c r="G2">
-        <v>-12.5673537477959</v>
+        <v>-9.821902568014938</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.43661505795803</v>
       </c>
       <c r="E3">
-        <v>-16.66127027169057</v>
+        <v>-15.03580718943579</v>
       </c>
       <c r="F3">
-        <v>3.427418855512212</v>
+        <v>4.678256947209077</v>
       </c>
       <c r="G3">
-        <v>-12.05735392952798</v>
+        <v>-9.424545935875202</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.62374889645159</v>
       </c>
       <c r="E4">
-        <v>-15.17492730918358</v>
+        <v>-16.1425383304308</v>
       </c>
       <c r="F4">
-        <v>3.749360533140628</v>
+        <v>4.381742835376993</v>
       </c>
       <c r="G4">
-        <v>-10.99772971696054</v>
+        <v>-8.918325170402927</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.78602083249801</v>
       </c>
       <c r="E5">
-        <v>-17.28565160263131</v>
+        <v>-15.30178299588914</v>
       </c>
       <c r="F5">
-        <v>2.74104190922657</v>
+        <v>4.769016193329402</v>
       </c>
       <c r="G5">
-        <v>-11.87010349521957</v>
+        <v>-9.320422914720126</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.93731657379498</v>
       </c>
       <c r="E6">
-        <v>-19.15376605653919</v>
+        <v>-17.14434689372667</v>
       </c>
       <c r="F6">
-        <v>3.315181699372101</v>
+        <v>5.175418211347256</v>
       </c>
       <c r="G6">
-        <v>-11.23783859163293</v>
+        <v>-9.041447885319828</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.11413218323476</v>
       </c>
       <c r="E7">
-        <v>-19.08105578587542</v>
+        <v>-18.5411881521836</v>
       </c>
       <c r="F7">
-        <v>3.515679745545694</v>
+        <v>5.182500752641191</v>
       </c>
       <c r="G7">
-        <v>-10.47702584586906</v>
+        <v>-8.699518666221721</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.30357741261434</v>
       </c>
       <c r="E8">
-        <v>-20.57733738308272</v>
+        <v>-18.41512988205241</v>
       </c>
       <c r="F8">
-        <v>3.746954954202899</v>
+        <v>5.411231216636997</v>
       </c>
       <c r="G8">
-        <v>-10.29988029850055</v>
+        <v>-8.618695235170037</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.52634449188087</v>
       </c>
       <c r="E9">
-        <v>-18.56621955683835</v>
+        <v>-19.0669182545257</v>
       </c>
       <c r="F9">
-        <v>3.456757972184565</v>
+        <v>5.4683405221208</v>
       </c>
       <c r="G9">
-        <v>-9.382787076140344</v>
+        <v>-8.052843757864439</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.763202161413902</v>
       </c>
       <c r="E10">
-        <v>-21.76756883776341</v>
+        <v>-19.64254503772429</v>
       </c>
       <c r="F10">
-        <v>3.688402632703419</v>
+        <v>5.56696925856772</v>
       </c>
       <c r="G10">
-        <v>-9.831408289071183</v>
+        <v>-7.817205783304327</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.013427398716962</v>
       </c>
       <c r="E11">
-        <v>-21.20977594399364</v>
+        <v>-20.46185318898454</v>
       </c>
       <c r="F11">
-        <v>3.732422076488184</v>
+        <v>5.866041368939649</v>
       </c>
       <c r="G11">
-        <v>-9.276093776935317</v>
+        <v>-7.950629191005467</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.276166070299874</v>
       </c>
       <c r="E12">
-        <v>-21.31406723357141</v>
+        <v>-21.99955476273436</v>
       </c>
       <c r="F12">
-        <v>3.905345428557387</v>
+        <v>6.272766450244594</v>
       </c>
       <c r="G12">
-        <v>-8.232212354252285</v>
+        <v>-6.788388356912018</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.539022530764115</v>
       </c>
       <c r="E13">
-        <v>-23.43122069814998</v>
+        <v>-23.48271636536653</v>
       </c>
       <c r="F13">
-        <v>4.330866166231853</v>
+        <v>6.412828467444741</v>
       </c>
       <c r="G13">
-        <v>-8.03291333365588</v>
+        <v>-6.259354905202596</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.821540127262287</v>
       </c>
       <c r="E14">
-        <v>-23.74025284640782</v>
+        <v>-23.56171044476477</v>
       </c>
       <c r="F14">
-        <v>4.769377361517022</v>
+        <v>6.863057748009911</v>
       </c>
       <c r="G14">
-        <v>-6.980627924134054</v>
+        <v>-6.084573387061335</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.119535715012407</v>
       </c>
       <c r="E15">
-        <v>-26.0395038615235</v>
+        <v>-24.0939195567736</v>
       </c>
       <c r="F15">
-        <v>4.401446382419983</v>
+        <v>6.857830749698246</v>
       </c>
       <c r="G15">
-        <v>-7.093341600366188</v>
+        <v>-5.479131273403799</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.443573239054583</v>
       </c>
       <c r="E16">
-        <v>-23.79181081179424</v>
+        <v>-25.57847248519958</v>
       </c>
       <c r="F16">
-        <v>4.918102445015646</v>
+        <v>7.258296686907639</v>
       </c>
       <c r="G16">
-        <v>-7.447322016496874</v>
+        <v>-4.678230544443386</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.797860557299378</v>
       </c>
       <c r="E17">
-        <v>-26.07873509569783</v>
+        <v>-26.39585354640511</v>
       </c>
       <c r="F17">
-        <v>5.180867212122871</v>
+        <v>7.268932924359585</v>
       </c>
       <c r="G17">
-        <v>-6.010268985253659</v>
+        <v>-4.457854982762922</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.175765699943078</v>
       </c>
       <c r="E18">
-        <v>-28.19395524040469</v>
+        <v>-27.53100511249593</v>
       </c>
       <c r="F18">
-        <v>5.125116429179658</v>
+        <v>8.078693538557408</v>
       </c>
       <c r="G18">
-        <v>-6.028559861858999</v>
+        <v>-4.340653436578664</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.587391221480741</v>
       </c>
       <c r="E19">
-        <v>-26.81627066918353</v>
+        <v>-28.08906381179049</v>
       </c>
       <c r="F19">
-        <v>5.532557219920624</v>
+        <v>7.975208912395277</v>
       </c>
       <c r="G19">
-        <v>-4.59792404082074</v>
+        <v>-3.695914395335691</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.026614940448328</v>
       </c>
       <c r="E20">
-        <v>-28.49831710252777</v>
+        <v>-28.61218777402625</v>
       </c>
       <c r="F20">
-        <v>5.951934784935929</v>
+        <v>8.148012979558477</v>
       </c>
       <c r="G20">
-        <v>-4.287305481603855</v>
+        <v>-3.249756419926569</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.503331896847364</v>
       </c>
       <c r="E21">
-        <v>-28.88085278481243</v>
+        <v>-29.85372592480821</v>
       </c>
       <c r="F21">
-        <v>5.477387950894176</v>
+        <v>8.476444087420424</v>
       </c>
       <c r="G21">
-        <v>-5.337064995733779</v>
+        <v>-2.666539574973181</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.025606964042494</v>
       </c>
       <c r="E22">
-        <v>-28.31747589841642</v>
+        <v>-30.02861350048542</v>
       </c>
       <c r="F22">
-        <v>6.832726247189004</v>
+        <v>8.434846789921444</v>
       </c>
       <c r="G22">
-        <v>-4.909665220211805</v>
+        <v>-2.287125285035869</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.60111380428327</v>
       </c>
       <c r="E23">
-        <v>-28.33437116208582</v>
+        <v>-30.16269992810751</v>
       </c>
       <c r="F23">
-        <v>6.016782698696685</v>
+        <v>8.662682617122226</v>
       </c>
       <c r="G23">
-        <v>-3.538645751911619</v>
+        <v>-1.896933841426442</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.248653218291113</v>
       </c>
       <c r="E24">
-        <v>-29.63170563041119</v>
+        <v>-30.75034610488014</v>
       </c>
       <c r="F24">
-        <v>6.247575797525462</v>
+        <v>8.67654948744509</v>
       </c>
       <c r="G24">
-        <v>-3.946399674385465</v>
+        <v>-1.572990041816514</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.972636788345594</v>
       </c>
       <c r="E25">
-        <v>-31.26009257343864</v>
+        <v>-30.96856828752061</v>
       </c>
       <c r="F25">
-        <v>6.678340100859649</v>
+        <v>8.126841565477726</v>
       </c>
       <c r="G25">
-        <v>-3.7944752251394</v>
+        <v>-1.512029155614019</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.7861478816315541</v>
       </c>
       <c r="E26">
-        <v>-30.49989084914769</v>
+        <v>-31.05963575224013</v>
       </c>
       <c r="F26">
-        <v>6.086809565459744</v>
+        <v>8.76176529890588</v>
       </c>
       <c r="G26">
-        <v>-4.488823635102707</v>
+        <v>-1.182088475678304</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.6917236051220764</v>
       </c>
       <c r="E27">
-        <v>-29.95420456638979</v>
+        <v>-30.93942312704863</v>
       </c>
       <c r="F27">
-        <v>6.450486049576006</v>
+        <v>8.541253896280653</v>
       </c>
       <c r="G27">
-        <v>-4.010874622807599</v>
+        <v>-1.703287082869796</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.6862590801592006</v>
       </c>
       <c r="E28">
-        <v>-30.22317276160267</v>
+        <v>-31.30656908476913</v>
       </c>
       <c r="F28">
-        <v>6.298508795653992</v>
+        <v>8.744399404673592</v>
       </c>
       <c r="G28">
-        <v>-2.593161987495351</v>
+        <v>-1.96188916685334</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.7675196829068482</v>
       </c>
       <c r="E29">
-        <v>-30.17000127361655</v>
+        <v>-30.85381090540427</v>
       </c>
       <c r="F29">
-        <v>6.309196391884911</v>
+        <v>8.333605382686095</v>
       </c>
       <c r="G29">
-        <v>-3.288489426680326</v>
+        <v>-2.066130976887312</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.9196808272507789</v>
       </c>
       <c r="E30">
-        <v>-28.28753539797573</v>
+        <v>-30.25790606791221</v>
       </c>
       <c r="F30">
-        <v>5.978028358124114</v>
+        <v>8.650472481604961</v>
       </c>
       <c r="G30">
-        <v>-3.735198269198173</v>
+        <v>-1.796125160529785</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.132881879244804</v>
       </c>
       <c r="E31">
-        <v>-29.45966923430848</v>
+        <v>-30.81966112528587</v>
       </c>
       <c r="F31">
-        <v>6.248203700016783</v>
+        <v>8.690742734524656</v>
       </c>
       <c r="G31">
-        <v>-4.0306457915961</v>
+        <v>-1.60637363290308</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.388146743369164</v>
       </c>
       <c r="E32">
-        <v>-30.51019704305025</v>
+        <v>-30.19039769443279</v>
       </c>
       <c r="F32">
-        <v>5.400409424886824</v>
+        <v>8.470073942092895</v>
       </c>
       <c r="G32">
-        <v>-4.587191269806674</v>
+        <v>-1.829336442473337</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.6658196772039</v>
       </c>
       <c r="E33">
-        <v>-29.21465468541155</v>
+        <v>-29.87190660738265</v>
       </c>
       <c r="F33">
-        <v>5.726564179125879</v>
+        <v>8.327319730833652</v>
       </c>
       <c r="G33">
-        <v>-4.362677677949296</v>
+        <v>-2.504370563951588</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.948447372345517</v>
       </c>
       <c r="E34">
-        <v>-29.33783893330596</v>
+        <v>-29.04090301303168</v>
       </c>
       <c r="F34">
-        <v>6.34726318751316</v>
+        <v>8.610737354027474</v>
       </c>
       <c r="G34">
-        <v>-5.172648133619237</v>
+        <v>-2.229939535512124</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.213639516586289</v>
       </c>
       <c r="E35">
-        <v>-29.38978107073993</v>
+        <v>-29.06401978726567</v>
       </c>
       <c r="F35">
-        <v>6.724619330919252</v>
+        <v>9.003353681727939</v>
       </c>
       <c r="G35">
-        <v>-5.404503139266826</v>
+        <v>-2.313778376566545</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.449638799590481</v>
       </c>
       <c r="E36">
-        <v>-28.64229855613126</v>
+        <v>-29.4612536844289</v>
       </c>
       <c r="F36">
-        <v>5.948545105523674</v>
+        <v>8.399352903446291</v>
       </c>
       <c r="G36">
-        <v>-5.38014750297633</v>
+        <v>-2.410553457069932</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.64564280797877</v>
       </c>
       <c r="E37">
-        <v>-27.97849286668958</v>
+        <v>-28.67895272267853</v>
       </c>
       <c r="F37">
-        <v>5.524932926345257</v>
+        <v>8.493684069807488</v>
       </c>
       <c r="G37">
-        <v>-4.298333266756718</v>
+        <v>-2.661829791730812</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.79904596413347</v>
       </c>
       <c r="E38">
-        <v>-27.47858327915394</v>
+        <v>-28.85828423447331</v>
       </c>
       <c r="F38">
-        <v>5.824548445733421</v>
+        <v>8.77003240558582</v>
       </c>
       <c r="G38">
-        <v>-5.116731205966773</v>
+        <v>-3.381267457214718</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.914529933499055</v>
       </c>
       <c r="E39">
-        <v>-26.664495714529</v>
+        <v>-28.15320393088548</v>
       </c>
       <c r="F39">
-        <v>6.737135962375553</v>
+        <v>8.517097046080213</v>
       </c>
       <c r="G39">
-        <v>-5.711260407233454</v>
+        <v>-3.012285702663495</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.995939022539182</v>
       </c>
       <c r="E40">
-        <v>-25.7009548403801</v>
+        <v>-26.89915215438181</v>
       </c>
       <c r="F40">
-        <v>7.071027668156755</v>
+        <v>8.963708017829955</v>
       </c>
       <c r="G40">
-        <v>-4.972213439125697</v>
+        <v>-2.792447954368801</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.054140783493547</v>
       </c>
       <c r="E41">
-        <v>-27.38912310721713</v>
+        <v>-27.11200008156795</v>
       </c>
       <c r="F41">
-        <v>6.509437644163635</v>
+        <v>8.881767571079834</v>
       </c>
       <c r="G41">
-        <v>-5.433143007431338</v>
+        <v>-2.771658595189766</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.094069521948995</v>
       </c>
       <c r="E42">
-        <v>-24.53600813624497</v>
+        <v>-25.9293025522305</v>
       </c>
       <c r="F42">
-        <v>6.998426235505795</v>
+        <v>9.067451094621759</v>
       </c>
       <c r="G42">
-        <v>-5.102596634750485</v>
+        <v>-3.066787606747576</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.121931624447598</v>
       </c>
       <c r="E43">
-        <v>-24.6018033100529</v>
+        <v>-26.07741852770786</v>
       </c>
       <c r="F43">
-        <v>6.519222319925503</v>
+        <v>8.95075235165017</v>
       </c>
       <c r="G43">
-        <v>-6.201790597713138</v>
+        <v>-3.47188640197226</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.142979566462048</v>
       </c>
       <c r="E44">
-        <v>-25.20949703789049</v>
+        <v>-24.83538406817258</v>
       </c>
       <c r="F44">
-        <v>6.954191416196301</v>
+        <v>8.924305893948393</v>
       </c>
       <c r="G44">
-        <v>-5.418922281643544</v>
+        <v>-3.554819314653565</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.156792609656643</v>
       </c>
       <c r="E45">
-        <v>-23.51935599567416</v>
+        <v>-24.38488938897976</v>
       </c>
       <c r="F45">
-        <v>6.632087378556936</v>
+        <v>8.704110927671035</v>
       </c>
       <c r="G45">
-        <v>-6.376480739793711</v>
+        <v>-3.438390548868277</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.171489952571165</v>
       </c>
       <c r="E46">
-        <v>-25.00940777589422</v>
+        <v>-24.36870017123558</v>
       </c>
       <c r="F46">
-        <v>6.97921805216968</v>
+        <v>9.390771175608435</v>
       </c>
       <c r="G46">
-        <v>-6.423166074571999</v>
+        <v>-3.197061151099538</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.187257258398307</v>
       </c>
       <c r="E47">
-        <v>-23.24185502779442</v>
+        <v>-23.84615973519095</v>
       </c>
       <c r="F47">
-        <v>6.368452825676771</v>
+        <v>9.414588395173725</v>
       </c>
       <c r="G47">
-        <v>-7.06562593578693</v>
+        <v>-3.504800059032426</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.211220380238815</v>
       </c>
       <c r="E48">
-        <v>-21.82204651071119</v>
+        <v>-22.25428367292007</v>
       </c>
       <c r="F48">
-        <v>6.497641692347771</v>
+        <v>9.219733187748004</v>
       </c>
       <c r="G48">
-        <v>-5.098403778937158</v>
+        <v>-3.545224828281224</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.25046029933606</v>
       </c>
       <c r="E49">
-        <v>-22.063377161163</v>
+        <v>-22.11763471391056</v>
       </c>
       <c r="F49">
-        <v>6.219484202161725</v>
+        <v>9.523782129475951</v>
       </c>
       <c r="G49">
-        <v>-6.150165734168465</v>
+        <v>-3.6583666666263</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.306368663575468</v>
       </c>
       <c r="E50">
-        <v>-19.68303469493004</v>
+        <v>-22.43607388581914</v>
       </c>
       <c r="F50">
-        <v>6.808844414966295</v>
+        <v>9.25534635912916</v>
       </c>
       <c r="G50">
-        <v>-5.39728965196158</v>
+        <v>-4.105709920079788</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.391965609547347</v>
       </c>
       <c r="E51">
-        <v>-21.13920042395083</v>
+        <v>-21.40646372591487</v>
       </c>
       <c r="F51">
-        <v>6.240108893756627</v>
+        <v>9.433097436421878</v>
       </c>
       <c r="G51">
-        <v>-6.871138517471945</v>
+        <v>-3.319813140284503</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.507897587626245</v>
       </c>
       <c r="E52">
-        <v>-20.33812487040657</v>
+        <v>-21.00620629090717</v>
       </c>
       <c r="F52">
-        <v>7.01605720730698</v>
+        <v>9.647112781874352</v>
       </c>
       <c r="G52">
-        <v>-6.289433293636812</v>
+        <v>-3.620197580704224</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.667805470980853</v>
       </c>
       <c r="E53">
-        <v>-21.48689066322017</v>
+        <v>-20.20774310728623</v>
       </c>
       <c r="F53">
-        <v>6.786529853869681</v>
+        <v>9.386864594936831</v>
       </c>
       <c r="G53">
-        <v>-6.243142181291782</v>
+        <v>-3.722027062736007</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.881407861842758</v>
       </c>
       <c r="E54">
-        <v>-19.26760142574141</v>
+        <v>-18.72861842606179</v>
       </c>
       <c r="F54">
-        <v>6.393136517545391</v>
+        <v>9.611657000299727</v>
       </c>
       <c r="G54">
-        <v>-6.858680044283153</v>
+        <v>-4.338690156646147</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.151693592350932</v>
       </c>
       <c r="E55">
-        <v>-19.52925789241694</v>
+        <v>-19.0336302657572</v>
       </c>
       <c r="F55">
-        <v>6.559320272425416</v>
+        <v>9.578464318469551</v>
       </c>
       <c r="G55">
-        <v>-6.589196376843848</v>
+        <v>-4.59055913032921</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.491564766727428</v>
       </c>
       <c r="E56">
-        <v>-16.32692430040789</v>
+        <v>-18.48661495537536</v>
       </c>
       <c r="F56">
-        <v>6.248046310210252</v>
+        <v>9.447527596578645</v>
       </c>
       <c r="G56">
-        <v>-6.875702099017211</v>
+        <v>-4.284799166796387</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.891275572111244</v>
       </c>
       <c r="E57">
-        <v>-18.03578801927654</v>
+        <v>-17.91767068919842</v>
       </c>
       <c r="F57">
-        <v>6.205817796750338</v>
+        <v>9.370429785665289</v>
       </c>
       <c r="G57">
-        <v>-6.215154999275048</v>
+        <v>-4.943061865021326</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.355023420753973</v>
       </c>
       <c r="E58">
-        <v>-18.60516837264259</v>
+        <v>-16.83097879284571</v>
       </c>
       <c r="F58">
-        <v>6.084548122450102</v>
+        <v>9.451187323764213</v>
       </c>
       <c r="G58">
-        <v>-7.714782356878065</v>
+        <v>-4.696121977126285</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.873861988096386</v>
       </c>
       <c r="E59">
-        <v>-17.2617955567815</v>
+        <v>-17.1091733470167</v>
       </c>
       <c r="F59">
-        <v>6.403999727665703</v>
+        <v>8.982336343984111</v>
       </c>
       <c r="G59">
-        <v>-8.133665883543827</v>
+        <v>-5.410027474821621</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.434106138144888</v>
       </c>
       <c r="E60">
-        <v>-14.79961821460412</v>
+        <v>-16.69579176422254</v>
       </c>
       <c r="F60">
-        <v>7.033247487649875</v>
+        <v>8.956479683873127</v>
       </c>
       <c r="G60">
-        <v>-8.052031816296601</v>
+        <v>-5.221035673870931</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.033446196801038</v>
       </c>
       <c r="E61">
-        <v>-17.08130114581578</v>
+        <v>-15.54809334671942</v>
       </c>
       <c r="F61">
-        <v>6.23342562555084</v>
+        <v>8.807472955457552</v>
       </c>
       <c r="G61">
-        <v>-8.221916882957231</v>
+        <v>-5.355314100425661</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.64622581923835</v>
       </c>
       <c r="E62">
-        <v>-15.55735500797379</v>
+        <v>-15.78299897925172</v>
       </c>
       <c r="F62">
-        <v>6.185938635817956</v>
+        <v>8.945483934968365</v>
       </c>
       <c r="G62">
-        <v>-6.852581344918312</v>
+        <v>-5.594638446348425</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.270305030322849</v>
       </c>
       <c r="E63">
-        <v>-14.97164838088984</v>
+        <v>-14.69778562613065</v>
       </c>
       <c r="F63">
-        <v>5.961323501079259</v>
+        <v>8.714861479824567</v>
       </c>
       <c r="G63">
-        <v>-7.415799886303772</v>
+        <v>-6.166412397758963</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.888611869162345</v>
       </c>
       <c r="E64">
-        <v>-14.73748617318468</v>
+        <v>-15.23285630074228</v>
       </c>
       <c r="F64">
-        <v>6.536586557422987</v>
+        <v>8.665777397739085</v>
       </c>
       <c r="G64">
-        <v>-8.350779319857695</v>
+        <v>-5.969478711762106</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.48655211495501</v>
       </c>
       <c r="E65">
-        <v>-13.44029291404436</v>
+        <v>-15.30215263169705</v>
       </c>
       <c r="F65">
-        <v>6.266833682905744</v>
+        <v>8.76450553827434</v>
       </c>
       <c r="G65">
-        <v>-8.052025289435125</v>
+        <v>-6.063290597154579</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.06135136575756</v>
       </c>
       <c r="E66">
-        <v>-15.27539349113118</v>
+        <v>-14.17497523134991</v>
       </c>
       <c r="F66">
-        <v>6.547209540996487</v>
+        <v>8.422297023769032</v>
       </c>
       <c r="G66">
-        <v>-8.207889352269179</v>
+        <v>-6.595942540867285</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.58924096434939</v>
       </c>
       <c r="E67">
-        <v>-14.71295730710025</v>
+        <v>-15.26216135985027</v>
       </c>
       <c r="F67">
-        <v>6.212650171088629</v>
+        <v>8.585881361739073</v>
       </c>
       <c r="G67">
-        <v>-8.480127355252108</v>
+        <v>-6.796962042149235</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.07288812638568</v>
       </c>
       <c r="E68">
-        <v>-13.31466657789095</v>
+        <v>-13.90503726129268</v>
       </c>
       <c r="F68">
-        <v>5.909724495558877</v>
+        <v>8.48490834554223</v>
       </c>
       <c r="G68">
-        <v>-7.633867549765692</v>
+        <v>-6.408005480731404</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.49783969814453</v>
       </c>
       <c r="E69">
-        <v>-16.56098683104126</v>
+        <v>-14.04698571795267</v>
       </c>
       <c r="F69">
-        <v>5.620089146639642</v>
+        <v>8.289085604990037</v>
       </c>
       <c r="G69">
-        <v>-7.902014515974346</v>
+        <v>-6.696435321668417</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.85706408985853</v>
       </c>
       <c r="E70">
-        <v>-15.09423041314216</v>
+        <v>-12.56808946335109</v>
       </c>
       <c r="F70">
-        <v>5.490747860366527</v>
+        <v>8.206113012456028</v>
       </c>
       <c r="G70">
-        <v>-8.627105748870308</v>
+        <v>-6.835209450409044</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.15249972719224</v>
       </c>
       <c r="E71">
-        <v>-13.90350472631381</v>
+        <v>-13.46211803955634</v>
       </c>
       <c r="F71">
-        <v>6.222156515403156</v>
+        <v>8.370587017016675</v>
       </c>
       <c r="G71">
-        <v>-8.816597507410197</v>
+        <v>-6.741298356722108</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.3676002033881</v>
       </c>
       <c r="E72">
-        <v>-12.63862760449198</v>
+        <v>-12.90629792116586</v>
       </c>
       <c r="F72">
-        <v>5.892834084215796</v>
+        <v>8.253926378945616</v>
       </c>
       <c r="G72">
-        <v>-8.526572501528014</v>
+        <v>-6.669810948328244</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.51404622236959</v>
       </c>
       <c r="E73">
-        <v>-11.41446441328744</v>
+        <v>-12.83538599100573</v>
       </c>
       <c r="F73">
-        <v>5.083119858592529</v>
+        <v>8.010709425809653</v>
       </c>
       <c r="G73">
-        <v>-8.376891987258011</v>
+        <v>-6.490149948546192</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.58307591558176</v>
       </c>
       <c r="E74">
-        <v>-14.41112267406833</v>
+        <v>-13.18663553238046</v>
       </c>
       <c r="F74">
-        <v>4.821980348329596</v>
+        <v>7.860544639764964</v>
       </c>
       <c r="G74">
-        <v>-8.229350978180426</v>
+        <v>-6.905524634481498</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.57710612892077</v>
       </c>
       <c r="E75">
-        <v>-13.32830157067036</v>
+        <v>-13.07015456756432</v>
       </c>
       <c r="F75">
-        <v>5.203095623009593</v>
+        <v>7.914029009494117</v>
       </c>
       <c r="G75">
-        <v>-8.212925478585436</v>
+        <v>-6.650394840804135</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.50165881505181</v>
       </c>
       <c r="E76">
-        <v>-14.4130912962363</v>
+        <v>-13.86949823198612</v>
       </c>
       <c r="F76">
-        <v>5.528400472293376</v>
+        <v>7.527695020176483</v>
       </c>
       <c r="G76">
-        <v>-7.585310311115576</v>
+        <v>-6.78278830976408</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.3439813531109</v>
       </c>
       <c r="E77">
-        <v>-14.50411722884257</v>
+        <v>-13.4387769919108</v>
       </c>
       <c r="F77">
-        <v>4.858723412848171</v>
+        <v>7.598194056359138</v>
       </c>
       <c r="G77">
-        <v>-7.102113702192328</v>
+        <v>-6.296466639565271</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.11638417821831</v>
       </c>
       <c r="E78">
-        <v>-15.97144678990449</v>
+        <v>-12.54444107806752</v>
       </c>
       <c r="F78">
-        <v>5.274141381678096</v>
+        <v>7.520576030716824</v>
       </c>
       <c r="G78">
-        <v>-7.281581506874638</v>
+        <v>-6.259250475418951</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.80698150377528</v>
       </c>
       <c r="E79">
-        <v>-14.83806033862673</v>
+        <v>-13.8009121001679</v>
       </c>
       <c r="F79">
-        <v>5.603977400655191</v>
+        <v>7.635167407015691</v>
       </c>
       <c r="G79">
-        <v>-6.643834039646667</v>
+        <v>-5.426853723711346</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.41762927555824</v>
       </c>
       <c r="E80">
-        <v>-15.85537283979818</v>
+        <v>-13.65455293308094</v>
       </c>
       <c r="F80">
-        <v>5.24252591138285</v>
+        <v>7.531462435124415</v>
       </c>
       <c r="G80">
-        <v>-7.691199500986539</v>
+        <v>-5.768568861752982</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.94957469825303</v>
       </c>
       <c r="E81">
-        <v>-17.51951062590976</v>
+        <v>-14.7153412504007</v>
       </c>
       <c r="F81">
-        <v>5.311016984981118</v>
+        <v>7.369299575617578</v>
       </c>
       <c r="G81">
-        <v>-7.38425425940935</v>
+        <v>-5.500301801293137</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.39256358862332</v>
       </c>
       <c r="E82">
-        <v>-17.69793673763572</v>
+        <v>-15.50852154921645</v>
       </c>
       <c r="F82">
-        <v>5.710522016003264</v>
+        <v>7.190186662314658</v>
       </c>
       <c r="G82">
-        <v>-6.169192840748498</v>
+        <v>-4.788892175426904</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.762497368639346</v>
       </c>
       <c r="E83">
-        <v>-17.68222513919389</v>
+        <v>-17.09306304028769</v>
       </c>
       <c r="F83">
-        <v>5.055566702040612</v>
+        <v>7.046822772646953</v>
       </c>
       <c r="G83">
-        <v>-6.452416856970832</v>
+        <v>-5.082851573407896</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.056585522985735</v>
       </c>
       <c r="E84">
-        <v>-20.55545826582352</v>
+        <v>-18.2428339102419</v>
       </c>
       <c r="F84">
-        <v>5.088613591207896</v>
+        <v>6.958979379784482</v>
       </c>
       <c r="G84">
-        <v>-6.241734989957172</v>
+        <v>-4.648267028771178</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.29215049798889</v>
       </c>
       <c r="E85">
-        <v>-20.43481163004858</v>
+        <v>-18.22310200323763</v>
       </c>
       <c r="F85">
-        <v>5.035419150069723</v>
+        <v>6.995850012883088</v>
       </c>
       <c r="G85">
-        <v>-6.262929014547829</v>
+        <v>-4.770985078276458</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.486739712409649</v>
       </c>
       <c r="E86">
-        <v>-19.83632557171814</v>
+        <v>-19.02935245809263</v>
       </c>
       <c r="F86">
-        <v>4.718184256024013</v>
+        <v>7.13220591432311</v>
       </c>
       <c r="G86">
-        <v>-5.947947901119194</v>
+        <v>-4.312752409133436</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.654752524524531</v>
       </c>
       <c r="E87">
-        <v>-24.47518020318153</v>
+        <v>-20.98170234409068</v>
       </c>
       <c r="F87">
-        <v>4.292751325294243</v>
+        <v>6.9816501388643</v>
       </c>
       <c r="G87">
-        <v>-4.545996330903497</v>
+        <v>-4.437068234328478</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.831298126665213</v>
       </c>
       <c r="E88">
-        <v>-23.13150420289373</v>
+        <v>-21.33978807130607</v>
       </c>
       <c r="F88">
-        <v>4.876856375295453</v>
+        <v>6.884348446996664</v>
       </c>
       <c r="G88">
-        <v>-5.576689577284521</v>
+        <v>-3.643535026604186</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.033006292655604</v>
       </c>
       <c r="E89">
-        <v>-23.4362253177964</v>
+        <v>-23.847272795826</v>
       </c>
       <c r="F89">
-        <v>4.146191594186537</v>
+        <v>6.424175444128288</v>
       </c>
       <c r="G89">
-        <v>-5.082355531935584</v>
+        <v>-3.576420615400437</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.291432493075934</v>
       </c>
       <c r="E90">
-        <v>-26.07214810253665</v>
+        <v>-26.03117667281722</v>
       </c>
       <c r="F90">
-        <v>4.698117884058598</v>
+        <v>6.517148087948893</v>
       </c>
       <c r="G90">
-        <v>-4.867467755385641</v>
+        <v>-3.699658203079348</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.62668708750943</v>
       </c>
       <c r="E91">
-        <v>-28.60491134778515</v>
+        <v>-26.73628812548998</v>
       </c>
       <c r="F91">
-        <v>4.678586637435391</v>
+        <v>6.215398694131117</v>
       </c>
       <c r="G91">
-        <v>-4.978105889667839</v>
+        <v>-3.240376014610699</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.049383830094359</v>
       </c>
       <c r="E92">
-        <v>-29.73379364138114</v>
+        <v>-28.83672283788046</v>
       </c>
       <c r="F92">
-        <v>3.88539999823278</v>
+        <v>5.885165058800678</v>
       </c>
       <c r="G92">
-        <v>-5.092558321797655</v>
+        <v>-3.423514526188113</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.574312112398269</v>
       </c>
       <c r="E93">
-        <v>-31.42958305099923</v>
+        <v>-31.00957294293064</v>
       </c>
       <c r="F93">
-        <v>3.391643324120107</v>
+        <v>5.826847993643593</v>
       </c>
       <c r="G93">
-        <v>-5.069797850452329</v>
+        <v>-3.286518314514035</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.192752282921478</v>
       </c>
       <c r="E94">
-        <v>-32.51512450781497</v>
+        <v>-32.6646068898182</v>
       </c>
       <c r="F94">
-        <v>3.756890392832076</v>
+        <v>5.322292722068025</v>
       </c>
       <c r="G94">
-        <v>-4.057643501412802</v>
+        <v>-3.267935034514491</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.902928222183756</v>
       </c>
       <c r="E95">
-        <v>-35.69317011999642</v>
+        <v>-34.31279634444243</v>
       </c>
       <c r="F95">
-        <v>3.73293566427792</v>
+        <v>4.823994937853205</v>
       </c>
       <c r="G95">
-        <v>-5.436834600283173</v>
+        <v>-3.344482065925932</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.690311715842498</v>
       </c>
       <c r="E96">
-        <v>-36.7876866664851</v>
+        <v>-37.12165677214288</v>
       </c>
       <c r="F96">
-        <v>3.471975081373992</v>
+        <v>4.483681727965501</v>
       </c>
       <c r="G96">
-        <v>-4.135501126608983</v>
+        <v>-4.111137658084713</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.53600812853802</v>
       </c>
       <c r="E97">
-        <v>-39.82509208357389</v>
+        <v>-39.68298165167223</v>
       </c>
       <c r="F97">
-        <v>2.542268523985606</v>
+        <v>4.044796110614267</v>
       </c>
       <c r="G97">
-        <v>-4.8353399324474</v>
+        <v>-4.137568836325144</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.4290785491395</v>
       </c>
       <c r="E98">
-        <v>-40.15821701072706</v>
+        <v>-42.07887789431667</v>
       </c>
       <c r="F98">
-        <v>2.626317994143255</v>
+        <v>3.767395748234379</v>
       </c>
       <c r="G98">
-        <v>-4.180035207844193</v>
+        <v>-4.385806264281968</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.34559749421555</v>
       </c>
       <c r="E99">
-        <v>-43.21830726807205</v>
+        <v>-44.1083300719545</v>
       </c>
       <c r="F99">
-        <v>1.627142889621297</v>
+        <v>3.602981386126733</v>
       </c>
       <c r="G99">
-        <v>-6.645233398747504</v>
+        <v>-3.9541744717778</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.280601668534521</v>
       </c>
       <c r="E100">
-        <v>-46.22695169673639</v>
+        <v>-46.71251401575041</v>
       </c>
       <c r="F100">
-        <v>1.943400310131703</v>
+        <v>3.151686825081563</v>
       </c>
       <c r="G100">
-        <v>-4.41974333322185</v>
+        <v>-4.350472446985841</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.215262280833928</v>
       </c>
       <c r="E101">
-        <v>-48.73724295380908</v>
+        <v>-49.2397503750284</v>
       </c>
       <c r="F101">
-        <v>1.0033027120426</v>
+        <v>2.669446114602608</v>
       </c>
       <c r="G101">
-        <v>-5.698916806806671</v>
+        <v>-4.284916650302987</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.158162130797323</v>
       </c>
       <c r="E102">
-        <v>-51.57423619672109</v>
+        <v>-51.75419276682025</v>
       </c>
       <c r="F102">
-        <v>1.514922300829242</v>
+        <v>2.301700689803796</v>
       </c>
       <c r="G102">
-        <v>-5.565922866590769</v>
+        <v>-4.745039498529974</v>
       </c>
     </row>
   </sheetData>
